--- a/teacher/assessment-template.xlsx
+++ b/teacher/assessment-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h02680\Documents\software-development-project-1\teacher\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h02680\Documents\repos\software-development-project-1.github.io\teacher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC9E32-E7AB-4561-A280-52B098E80004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24BCE45-7097-41DB-B588-D56AA11DA5F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{F3B1C888-A306-445B-925E-DC4F729ADDF2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{F3B1C888-A306-445B-925E-DC4F729ADDF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -99,15 +99,9 @@
     <t>Documentation has project description</t>
   </si>
   <si>
-    <t>Documentation has developer guide</t>
-  </si>
-  <si>
     <t>Documentation has data model</t>
   </si>
   <si>
-    <t>Documentation has architecture description</t>
-  </si>
-  <si>
     <t>Documentation has relevant links</t>
   </si>
   <si>
@@ -154,6 +148,12 @@
   </si>
   <si>
     <t>https://github.com/</t>
+  </si>
+  <si>
+    <t>Documentation has implementation technologies</t>
+  </si>
+  <si>
+    <t>Documentation has technical instructions</t>
   </si>
 </sst>
 </file>
@@ -575,13 +575,13 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>13</v>
@@ -601,13 +601,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -725,7 +725,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -736,7 +736,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -758,7 +758,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -780,18 +780,18 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -857,7 +857,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -868,7 +868,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>0</v>
